--- a/テスト.xlsx
+++ b/テスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git検証\first-git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D285DE7D-C2FC-4572-B224-AD650718EBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4B68F6-30CB-4400-ADAF-9646851DB5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>test2</t>
+    <t>test1</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>

--- a/テスト.xlsx
+++ b/テスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git検証\first-git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D285DE7D-C2FC-4572-B224-AD650718EBEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D82979C-57D8-4AFB-BA5C-829F6E67F8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>test2</t>
+    <t>test2test2</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>

--- a/テスト.xlsx
+++ b/テスト.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git検証\first-git\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zns_r\Desktop\学習\git検証\first-git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE42E96-BF32-4055-AA12-2DE0313865A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C907D26B-868B-4018-9052-765446855130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>test1test2</t>
+    <t>test1test2test2</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -354,9 +354,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.649999999999999" x14ac:dyDescent="0.7"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
